--- a/output/pdf_financials_xlsx/CVW.xlsx
+++ b/output/pdf_financials_xlsx/CVW.xlsx
@@ -1033,16 +1033,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.991625</v>
+        <v>-2.991625</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.461313</v>
+        <v>-2.461313</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.93098</v>
+        <v>-2.93098</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.036297</v>
+        <v>-3.036297</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-7.612111</v>
@@ -1051,10 +1051,10 @@
         <v>-7.612111</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.271877</v>
+        <v>-2.271877</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.404603</v>
+        <v>-4.404603</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-3.701339</v>
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.991625</v>
+        <v>-2.991625</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.461313</v>
+        <v>-2.461313</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.93098</v>
+        <v>-2.93098</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.036297</v>
+        <v>-3.036297</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-7.612111</v>
@@ -1259,10 +1259,10 @@
         <v>-7.612111</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.271877</v>
+        <v>-2.271877</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.404603</v>
+        <v>-4.404603</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-3.701339</v>
@@ -1367,16 +1367,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.991625</v>
+        <v>-2.991625</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.461313</v>
+        <v>-2.461313</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.93098</v>
+        <v>-2.93098</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.036297</v>
+        <v>-3.036297</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-7.612111</v>
@@ -1385,10 +1385,10 @@
         <v>-7.612111</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.271877</v>
+        <v>-2.271877</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.404603</v>
+        <v>-4.404603</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-3.701339</v>
@@ -1502,13 +1502,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>61.532825</v>
+        <v>-61.532825</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>58.6196</v>
+        <v>-58.6196</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>75.907425</v>
+        <v>-75.907425</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>84.57901099999999</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>113.59385</v>
+        <v>-113.59385</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>110.115075</v>
+        <v>-110.115075</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>123.377967</v>
@@ -1543,16 +1543,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.991625</v>
+        <v>-2.991625</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.461313</v>
+        <v>-2.461313</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.93098</v>
+        <v>-2.93098</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.036297</v>
+        <v>-3.036297</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-7.612111</v>
@@ -1561,10 +1561,10 @@
         <v>-7.612111</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.271877</v>
+        <v>-2.271877</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.404603</v>
+        <v>-4.404603</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-3.701339</v>
@@ -1627,16 +1627,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.998989</v>
+        <v>-2.984261</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.467858</v>
+        <v>-2.454768</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.93098</v>
+        <v>-2.93098</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.036297</v>
+        <v>-3.036297</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-7.612111</v>
@@ -1645,10 +1645,10 @@
         <v>-7.612111</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.271877</v>
+        <v>-2.271877</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.404603</v>
+        <v>-4.404603</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-3.701339</v>
@@ -1731,16 +1731,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -1749,10 +1749,10 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -4481,10 +4481,10 @@
         <v>0.00325</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>2.271877</v>
+        <v>-2.271877</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>4.404603</v>
+        <v>-4.404603</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-3.701339</v>
@@ -11690,10 +11690,10 @@
         </is>
       </c>
       <c r="K81" s="5" t="n">
-        <v>2.271877</v>
+        <v>-2.271877</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>4.404603</v>
+        <v>-4.404603</v>
       </c>
       <c r="M81" s="5" t="n">
         <v>-3.701339</v>
@@ -21817,10 +21817,10 @@
         </is>
       </c>
       <c r="K224" s="5" t="n">
-        <v>2.271877</v>
+        <v>-2.271877</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>4.404603</v>
+        <v>-4.404603</v>
       </c>
       <c r="M224" s="5" t="n">
         <v>-3.701339</v>
@@ -24620,10 +24620,10 @@
         </is>
       </c>
       <c r="H264" s="5" t="n">
-        <v>3.036297</v>
+        <v>-3.036297</v>
       </c>
       <c r="I264" s="5" t="n">
-        <v>1.454953</v>
+        <v>-1.454953</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="H291" s="5" t="n">
-        <v>3.026735</v>
+        <v>-3.026735</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
@@ -28185,16 +28185,16 @@
         </is>
       </c>
       <c r="E314" s="5" t="n">
-        <v>2.991625</v>
+        <v>-2.991625</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>2.461313</v>
+        <v>-2.461313</v>
       </c>
       <c r="G314" s="5" t="n">
-        <v>2.93098</v>
+        <v>-2.93098</v>
       </c>
       <c r="H314" s="5" t="n">
-        <v>3.026735</v>
+        <v>-3.026735</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CVW.xlsx
+++ b/output/pdf_financials_xlsx/CVW.xlsx
@@ -805,10 +805,10 @@
         <v>1.027505</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.488221</v>
+        <v>3.997639</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.864944</v>
+        <v>4.621767</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.053006</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.099174</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1561,10 +1561,10 @@
         <v>-7.612111</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.271877</v>
+        <v>-2.218871</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-4.404603</v>
+        <v>-4.305429</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-3.701339</v>
@@ -1645,10 +1645,10 @@
         <v>-7.612111</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.271877</v>
+        <v>-2.218871</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.404603</v>
+        <v>-4.305429</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-3.701339</v>
@@ -21503,7 +21503,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -22071,7 +22071,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
